--- a/data/trans_camb/P38C-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Clase-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 4,42</t>
+          <t>-5,42; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,2</t>
+          <t>-6,22; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,13</t>
+          <t>-4,78; 1,83</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 5,33</t>
+          <t>-6,12; 5,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 2,45</t>
+          <t>-6,68; 2,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,44</t>
+          <t>-5,33; 2,09</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,47</t>
+          <t>-5,88; 4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 4,3</t>
+          <t>-5,34; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,21</t>
+          <t>-4,26; 2,89</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,4</t>
+          <t>-6,69; 5,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 5,03</t>
+          <t>-5,87; 4,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,78</t>
+          <t>-4,81; 3,42</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-65,9; 1,7</t>
+          <t>-63,72; 2,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 10,15</t>
+          <t>-2,42; 10,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-61,02; 2,57</t>
+          <t>-58,66; 2,35</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,6; 2,12</t>
+          <t>-73,69; 2,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 12,44</t>
+          <t>-2,68; 12,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,46; 3,02</t>
+          <t>-66,03; 2,82</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 1,35</t>
+          <t>-6,11; 1,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,94</t>
+          <t>1,58; 11,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,07</t>
+          <t>-1,43; 6,22</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 1,62</t>
+          <t>-7,21; 1,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 11,89</t>
+          <t>1,77; 13,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 7,34</t>
+          <t>-1,68; 7,41</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,05</t>
+          <t>-6,62; 4,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 3,43</t>
+          <t>-27,77; 3,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 2,51</t>
+          <t>-17,43; 2,36</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 6,38</t>
+          <t>-8,09; 6,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 3,93</t>
+          <t>-31,5; 3,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 3,01</t>
+          <t>-20,43; 2,83</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 4,14</t>
+          <t>-19,67; 4,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,7</t>
+          <t>-9,07; -1,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -2,36</t>
+          <t>-11,63; -2,78</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 7,68</t>
+          <t>-33,9; 9,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -2,02</t>
+          <t>-10,32; -1,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -2,96</t>
+          <t>-14,25; -3,53</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-26,0; -0,67</t>
+          <t>-22,42; -0,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 1,69</t>
+          <t>-7,17; 1,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,83; -0,25</t>
+          <t>-13,93; -0,17</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,46; -0,86</t>
+          <t>-27,32; -0,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,93</t>
+          <t>-8,2; 1,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -0,31</t>
+          <t>-16,41; -0,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38C-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-2,65</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,27</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,56</t>
+          <t>-4,95; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 1,87</t>
+          <t>-6,63; 1,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 1,83</t>
+          <t>-4,79; 2,23</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0,28%</t>
+          <t>-0,36%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-2,65%</t>
+          <t>-2,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,29%</t>
+          <t>-1,44%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 5,42</t>
+          <t>-5,58; 5,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,06</t>
+          <t>-7,12; 1,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 2,09</t>
+          <t>-5,27; 2,6</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-1,03</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,56</t>
+          <t>-5,84; 3,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,09</t>
+          <t>-5,32; 4,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,89</t>
+          <t>-4,64; 2,48</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-0,76%</t>
+          <t>-1,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0,63%</t>
+          <t>-0,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,8%</t>
+          <t>-1,18%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,49</t>
+          <t>-6,62; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 4,8</t>
+          <t>-5,88; 4,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,42</t>
+          <t>-5,23; 2,9</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-31,24</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-24,37</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 2,01</t>
+          <t>-5,59; 3,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 10,47</t>
+          <t>-3,41; 9,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 2,35</t>
+          <t>-3,28; 4,55</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-36,19%</t>
+          <t>-0,82%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-28,08%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,69; 2,36</t>
+          <t>-6,36; 4,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 12,49</t>
+          <t>-3,74; 10,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 2,82</t>
+          <t>-3,72; 5,37</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>-0,25</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,46</t>
+          <t>-6,03; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 11,67</t>
+          <t>-0,48; 6,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,22</t>
+          <t>-3,01; 1,94</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-3,05%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>-0,29%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,74</t>
+          <t>-7,04; 1,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 13,84</t>
+          <t>-0,55; 7,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,41</t>
+          <t>-3,47; 2,32</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,79</t>
+          <t>-10,87; 0,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 3,34</t>
+          <t>-1,7; 4,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 2,36</t>
+          <t>-3,41; 2,2</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-1,14%</t>
+          <t>-5,94%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-5,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,53%</t>
+          <t>-0,77%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 6,08</t>
+          <t>-13,28; 0,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 3,86</t>
+          <t>-1,86; 5,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 2,83</t>
+          <t>-4,0; 2,66</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>-12,49</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>-7,08</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,93</t>
+          <t>-8,76</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 4,43</t>
+          <t>-23,28; 0,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -1,59</t>
+          <t>-10,6; -3,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,63; -2,78</t>
+          <t>-12,92; -4,55</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-14,28%</t>
+          <t>-22,99%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-5,87%</t>
+          <t>-8,12%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-8,62%</t>
+          <t>-10,9%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 9,11</t>
+          <t>-41,07; 0,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -1,82</t>
+          <t>-12,07; -3,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -3,53</t>
+          <t>-15,85; -5,68</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>-2,21</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>-1,45</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-22,42; -0,51</t>
+          <t>-4,5; -0,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 1,68</t>
+          <t>-2,25; 0,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -0,17</t>
+          <t>-2,93; -0,15</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-8,57%</t>
+          <t>-2,71%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-1,17%</t>
+          <t>-0,85%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-4,62%</t>
+          <t>-1,72%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,32; -0,64</t>
+          <t>-5,45; -0,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 1,91</t>
+          <t>-2,55; 1,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,41; -0,2</t>
+          <t>-3,44; -0,18</t>
         </is>
       </c>
     </row>
